--- a/组合实盘追踪/20260616_银河.xlsx
+++ b/组合实盘追踪/20260616_银河.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>693</v>
+        <v>698.2</v>
       </c>
       <c r="D2" s="1">
-        <v>5.2</v>
+        <v>10.4</v>
       </c>
       <c r="E2" s="2">
-        <v>0.0076</v>
+        <v>0.0151</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,28 +553,28 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>-18.1</v>
+        <v>-12.9</v>
       </c>
       <c r="K2" s="2">
-        <v>-0.0254</v>
+        <v>-0.0181</v>
       </c>
       <c r="L2" s="1">
-        <v>-18.1</v>
+        <v>-12.9</v>
       </c>
       <c r="M2" s="2">
         <v/>
       </c>
       <c r="N2" s="1">
-        <v>31.6</v>
+        <v>36.4</v>
       </c>
       <c r="O2" s="1">
-        <v>16</v>
+        <v>21.6</v>
       </c>
       <c r="P2" s="1">
-        <v>-18.5</v>
+        <v>-12.9</v>
       </c>
       <c r="Q2" s="2">
-        <v>0.0237</v>
+        <v>0.0239</v>
       </c>
       <c r="R2" s="3">
         <v>200</v>
@@ -583,28 +583,28 @@
         <v>27</v>
       </c>
       <c r="T2" s="2">
-        <v>0.0076</v>
+        <v>0.0151</v>
       </c>
       <c r="U2" s="5">
-        <v>3.465</v>
+        <v>3.491</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v>0.0263</v>
+        <v>0.0186</v>
       </c>
       <c r="X2" s="2">
-        <v>-0.0065</v>
+        <v>0.0009</v>
       </c>
       <c r="Y2" s="2">
-        <v>0.0529</v>
+        <v>0.0608</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.1824</v>
+        <v>0.1912</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.4266</v>
+        <v>0.4373</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>805.6</v>
+        <v>806</v>
       </c>
       <c r="D3" s="1">
-        <v>-1.2</v>
+        <v>-0.8</v>
       </c>
       <c r="E3" s="2">
-        <v>-0.0015</v>
+        <v>-0.001</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,19 +636,19 @@
         <v/>
       </c>
       <c r="J3" s="1">
-        <v>-57.3</v>
+        <v>-56.9</v>
       </c>
       <c r="K3" s="2">
-        <v>-0.0664</v>
+        <v>-0.0659</v>
       </c>
       <c r="L3" s="1">
-        <v>-57.3</v>
+        <v>-56.9</v>
       </c>
       <c r="M3" s="2">
         <v/>
       </c>
       <c r="N3" s="1">
-        <v>-1.2</v>
+        <v>-0.8</v>
       </c>
       <c r="O3" s="1">
         <v>-24.8</v>
@@ -657,7 +657,7 @@
         <v>-56.9</v>
       </c>
       <c r="Q3" s="2">
-        <v>0.0276</v>
+        <v>0.0275</v>
       </c>
       <c r="R3" s="3">
         <v>400</v>
@@ -666,28 +666,28 @@
         <v>27</v>
       </c>
       <c r="T3" s="2">
-        <v>-0.0015</v>
+        <v>-0.001</v>
       </c>
       <c r="U3" s="5">
-        <v>2.014</v>
+        <v>2.015</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
       </c>
       <c r="W3" s="2">
-        <v>0.071</v>
+        <v>0.0705</v>
       </c>
       <c r="X3" s="2">
-        <v>-0.0359</v>
+        <v>-0.0355</v>
       </c>
       <c r="Y3" s="2">
-        <v>-0.1323</v>
+        <v>-0.1319</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0323</v>
+        <v>0.0328</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.0198</v>
+        <v>0.0203</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>674.3</v>
+        <v>669.9</v>
       </c>
       <c r="D4" s="1">
-        <v>-8.8</v>
+        <v>-13.2</v>
       </c>
       <c r="E4" s="2">
-        <v>-0.0129</v>
+        <v>-0.0193</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,28 +719,28 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>-62.8</v>
+        <v>-67.2</v>
       </c>
       <c r="K4" s="2">
-        <v>-0.0852</v>
+        <v>-0.0912</v>
       </c>
       <c r="L4" s="1">
-        <v>-62.8</v>
+        <v>-67.2</v>
       </c>
       <c r="M4" s="2">
         <v/>
       </c>
       <c r="N4" s="1">
-        <v>-1.1</v>
+        <v>-5.5</v>
       </c>
       <c r="O4" s="1">
-        <v>-27.5</v>
+        <v>-33</v>
       </c>
       <c r="P4" s="1">
-        <v>-61.7</v>
+        <v>-67.2</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.0231</v>
+        <v>0.0229</v>
       </c>
       <c r="R4" s="3">
         <v>1100</v>
@@ -749,28 +749,28 @@
         <v>27</v>
       </c>
       <c r="T4" s="2">
-        <v>-0.0129</v>
+        <v>-0.0193</v>
       </c>
       <c r="U4" s="5">
-        <v>0.613</v>
+        <v>0.609</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
       </c>
       <c r="W4" s="2">
-        <v>0.093</v>
+        <v>0.1002</v>
       </c>
       <c r="X4" s="2">
-        <v>-0.0554</v>
+        <v>-0.0616</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.0754</v>
+        <v>-0.0814</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1881</v>
+        <v>-0.1934</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.1498</v>
+        <v>-0.1553</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>983.6</v>
+        <v>982</v>
       </c>
       <c r="D5" s="1">
-        <v>-0.2</v>
+        <v>-1.8</v>
       </c>
       <c r="E5" s="2">
-        <v>-0.0002</v>
+        <v>-0.0018</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,28 +802,28 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>-7.7</v>
+        <v>-9.3</v>
       </c>
       <c r="K5" s="2">
-        <v>-0.0078</v>
+        <v>-0.0094</v>
       </c>
       <c r="L5" s="1">
-        <v>-7.7</v>
+        <v>-9.3</v>
       </c>
       <c r="M5" s="2">
         <v/>
       </c>
       <c r="N5" s="1">
-        <v>20</v>
+        <v>18.4</v>
       </c>
       <c r="O5" s="1">
-        <v>-1.2</v>
+        <v>-2.6</v>
       </c>
       <c r="P5" s="1">
-        <v>-7.9</v>
+        <v>-9.3</v>
       </c>
       <c r="Q5" s="2">
-        <v>0.0337</v>
+        <v>0.0336</v>
       </c>
       <c r="R5" s="3">
         <v>200</v>
@@ -832,28 +832,28 @@
         <v>27</v>
       </c>
       <c r="T5" s="2">
-        <v>-0.0002</v>
+        <v>-0.0018</v>
       </c>
       <c r="U5" s="5">
-        <v>4.918</v>
+        <v>4.91</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
       </c>
       <c r="W5" s="2">
-        <v>0.0079</v>
+        <v>0.0096</v>
       </c>
       <c r="X5" s="2">
-        <v>0.0082</v>
+        <v>0.0066</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0515</v>
+        <v>0.0498</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0812</v>
+        <v>0.0794</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.2964</v>
+        <v>0.2943</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>892.9</v>
+        <v>894.9</v>
       </c>
       <c r="D6" s="1">
-        <v>0.1</v>
+        <v>2.1</v>
       </c>
       <c r="E6" s="2">
-        <v>0.0001</v>
+        <v>0.0024</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,25 +885,25 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>-80.8</v>
+        <v>-78.8</v>
       </c>
       <c r="K6" s="2">
-        <v>-0.083</v>
+        <v>-0.0809</v>
       </c>
       <c r="L6" s="1">
-        <v>-80.8</v>
+        <v>-78.8</v>
       </c>
       <c r="M6" s="2">
         <v/>
       </c>
       <c r="N6" s="1">
-        <v>26.9</v>
+        <v>29</v>
       </c>
       <c r="O6" s="1">
-        <v>-46.8</v>
+        <v>-44.8</v>
       </c>
       <c r="P6" s="1">
-        <v>-80.8</v>
+        <v>-78.8</v>
       </c>
       <c r="Q6" s="2">
         <v>0.0306</v>
@@ -915,28 +915,28 @@
         <v>27</v>
       </c>
       <c r="T6" s="2">
-        <v>0.0001</v>
+        <v>0.0024</v>
       </c>
       <c r="U6" s="5">
-        <v>8.929</v>
+        <v>8.949</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
       </c>
       <c r="W6" s="2">
-        <v>0.0905</v>
+        <v>0.0881</v>
       </c>
       <c r="X6" s="2">
-        <v>-0.0654</v>
+        <v>-0.0633</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.1734</v>
+        <v>-0.1716</v>
       </c>
       <c r="Z6" s="2">
-        <v>-0.0451</v>
+        <v>-0.043</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.1767</v>
+        <v>0.1794</v>
       </c>
     </row>
     <row r="7">
@@ -947,46 +947,46 @@
         <v>中欧纯债</v>
       </c>
       <c r="C7" s="1">
-        <v>3021.3</v>
+        <v>3026.7</v>
       </c>
       <c r="D7" s="1">
+        <v>2.7</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0.0009</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" s="2">
+        <v/>
+      </c>
+      <c r="H7" s="1">
+        <v/>
+      </c>
+      <c r="I7" s="2">
+        <v/>
+      </c>
+      <c r="J7" s="1">
+        <v>7.95</v>
+      </c>
+      <c r="K7" s="2">
+        <v>0.0026</v>
+      </c>
+      <c r="L7" s="1">
+        <v>7.95</v>
+      </c>
+      <c r="M7" s="2">
+        <v/>
+      </c>
+      <c r="N7" s="1">
+        <v>2.7</v>
+      </c>
+      <c r="O7" s="1">
         <v>-2.7</v>
       </c>
-      <c r="E7" s="2">
-        <v>-0.0009</v>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" s="2">
-        <v/>
-      </c>
-      <c r="H7" s="1">
-        <v/>
-      </c>
-      <c r="I7" s="2">
-        <v/>
-      </c>
-      <c r="J7" s="1">
-        <v>2.55</v>
-      </c>
-      <c r="K7" s="2">
-        <v>0.0008</v>
-      </c>
-      <c r="L7" s="1">
-        <v>2.55</v>
-      </c>
-      <c r="M7" s="2">
-        <v/>
-      </c>
-      <c r="N7" s="1">
-        <v>-2.7</v>
-      </c>
-      <c r="O7" s="1">
-        <v>-8.1</v>
-      </c>
       <c r="P7" s="1">
-        <v>2.55</v>
+        <v>7.95</v>
       </c>
       <c r="Q7" s="2">
         <v>0.1034</v>
@@ -998,10 +998,10 @@
         <v>27</v>
       </c>
       <c r="T7" s="2">
-        <v>-0.0009</v>
+        <v>0.0009</v>
       </c>
       <c r="U7" s="5">
-        <v>1.119</v>
+        <v>1.121</v>
       </c>
       <c r="V7" s="5">
         <v>1.118</v>
@@ -1010,16 +1010,16 @@
         <v/>
       </c>
       <c r="X7" s="2">
-        <v>0</v>
+        <v>0.0018</v>
       </c>
       <c r="Y7" s="2">
-        <v>0.0072</v>
+        <v>0.009</v>
       </c>
       <c r="Z7" s="2">
-        <v>0.0118</v>
+        <v>0.0136</v>
       </c>
       <c r="AA7" s="2">
-        <v>0.0161</v>
+        <v>0.0179</v>
       </c>
     </row>
     <row r="8">
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>819.2</v>
+        <v>822.2</v>
       </c>
       <c r="D8" s="1">
-        <v>10.2</v>
+        <v>13.2</v>
       </c>
       <c r="E8" s="2">
-        <v>0.0126</v>
+        <v>0.0163</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,28 +1051,28 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>32.5</v>
+        <v>35.5</v>
       </c>
       <c r="K8" s="2">
-        <v>0.0413</v>
+        <v>0.0451</v>
       </c>
       <c r="L8" s="1">
-        <v>32.5</v>
+        <v>35.5</v>
       </c>
       <c r="M8" s="2">
         <v/>
       </c>
       <c r="N8" s="1">
-        <v>49.6</v>
+        <v>53</v>
       </c>
       <c r="O8" s="1">
-        <v>7.8</v>
+        <v>11.6</v>
       </c>
       <c r="P8" s="1">
-        <v>31.7</v>
+        <v>35.5</v>
       </c>
       <c r="Q8" s="2">
-        <v>0.028</v>
+        <v>0.0281</v>
       </c>
       <c r="R8" s="3">
         <v>200</v>
@@ -1081,10 +1081,10 @@
         <v>27</v>
       </c>
       <c r="T8" s="2">
-        <v>0.0126</v>
+        <v>0.0163</v>
       </c>
       <c r="U8" s="5">
-        <v>4.096</v>
+        <v>4.111</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
@@ -1093,16 +1093,16 @@
         <v/>
       </c>
       <c r="X8" s="2">
-        <v>0.0317</v>
+        <v>0.0355</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.2413</v>
+        <v>0.2458</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.3128</v>
+        <v>0.3177</v>
       </c>
       <c r="AA8" s="2">
-        <v>1.0277</v>
+        <v>1.0352</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>19868.8</v>
+        <v>19906.6</v>
       </c>
       <c r="D9" s="1">
-        <v>42</v>
+        <v>79.8</v>
       </c>
       <c r="E9" s="2">
-        <v>0.0021</v>
+        <v>0.004</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,28 +1134,28 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-508.84</v>
+        <v>-471.04</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.025</v>
+        <v>-0.0231</v>
       </c>
       <c r="L9" s="1">
-        <v>-508.84</v>
+        <v>-471.04</v>
       </c>
       <c r="M9" s="2">
         <v/>
       </c>
       <c r="N9" s="1">
-        <v>368.2</v>
+        <v>406</v>
       </c>
       <c r="O9" s="1">
-        <v>270.2</v>
+        <v>306.6</v>
       </c>
       <c r="P9" s="1">
-        <v>-507.44</v>
+        <v>-471.04</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.6801</v>
+        <v>0.6802</v>
       </c>
       <c r="R9" s="3">
         <v>1400</v>
@@ -1164,28 +1164,28 @@
         <v>27</v>
       </c>
       <c r="T9" s="2">
-        <v>0.0021</v>
+        <v>0.004</v>
       </c>
       <c r="U9" s="5">
-        <v>14.192</v>
+        <v>14.219</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0256</v>
+        <v>0.0236</v>
       </c>
       <c r="X9" s="2">
-        <v>0.0051</v>
+        <v>0.007</v>
       </c>
       <c r="Y9" s="2">
-        <v>0.0064</v>
+        <v>0.0083</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.06</v>
+        <v>0.0621</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.1683</v>
+        <v>0.1705</v>
       </c>
     </row>
     <row r="10">
@@ -1196,13 +1196,13 @@
         <v>能源化工</v>
       </c>
       <c r="C10" s="1">
-        <v>606.8</v>
+        <v>608</v>
       </c>
       <c r="D10" s="1">
-        <v>-14</v>
+        <v>-12.8</v>
       </c>
       <c r="E10" s="2">
-        <v>-0.0226</v>
+        <v>-0.0206</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -1217,25 +1217,25 @@
         <v/>
       </c>
       <c r="J10" s="1">
-        <v>-65.3</v>
+        <v>-64.1</v>
       </c>
       <c r="K10" s="2">
-        <v>-0.0972</v>
+        <v>-0.0954</v>
       </c>
       <c r="L10" s="1">
-        <v>-65.3</v>
+        <v>-64.1</v>
       </c>
       <c r="M10" s="2">
         <v/>
       </c>
       <c r="N10" s="1">
-        <v>-59.2</v>
+        <v>-58</v>
       </c>
       <c r="O10" s="1">
-        <v>-27.6</v>
+        <v>-26</v>
       </c>
       <c r="P10" s="1">
-        <v>-65.7</v>
+        <v>-64.1</v>
       </c>
       <c r="Q10" s="2">
         <v>0.0208</v>
@@ -1247,28 +1247,28 @@
         <v>27</v>
       </c>
       <c r="T10" s="2">
-        <v>-0.0226</v>
+        <v>-0.0206</v>
       </c>
       <c r="U10" s="5">
-        <v>1.517</v>
+        <v>1.52</v>
       </c>
       <c r="V10" s="5">
         <v>1.68</v>
       </c>
       <c r="W10" s="2">
-        <v>0.1074</v>
+        <v>0.1053</v>
       </c>
       <c r="X10" s="2">
-        <v>-0.08</v>
+        <v>-0.0782</v>
       </c>
       <c r="Y10" s="2">
-        <v>-0.0745</v>
+        <v>-0.0726</v>
       </c>
       <c r="Z10" s="2">
-        <v>0.2791</v>
+        <v>0.2816</v>
       </c>
       <c r="AA10" s="2">
-        <v>0.138</v>
+        <v>0.1403</v>
       </c>
     </row>
     <row r="11">
@@ -1279,13 +1279,13 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>850.8</v>
+        <v>851.2</v>
       </c>
       <c r="D11" s="1">
-        <v>-10.4</v>
+        <v>-10</v>
       </c>
       <c r="E11" s="2">
-        <v>-0.0121</v>
+        <v>-0.0116</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1300,25 +1300,25 @@
         <v/>
       </c>
       <c r="J11" s="1">
-        <v>-9.7</v>
+        <v>-9.3</v>
       </c>
       <c r="K11" s="2">
-        <v>-0.0113</v>
+        <v>-0.0108</v>
       </c>
       <c r="L11" s="1">
-        <v>-9.7</v>
+        <v>-9.3</v>
       </c>
       <c r="M11" s="2">
         <v/>
       </c>
       <c r="N11" s="1">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="O11" s="1">
-        <v>-8.8</v>
+        <v>-8.4</v>
       </c>
       <c r="P11" s="1">
-        <v>-9.7</v>
+        <v>-9.3</v>
       </c>
       <c r="Q11" s="2">
         <v>0.0291</v>
@@ -1330,28 +1330,28 @@
         <v>27</v>
       </c>
       <c r="T11" s="2">
-        <v>-0.0121</v>
+        <v>-0.0116</v>
       </c>
       <c r="U11" s="5">
-        <v>2.127</v>
+        <v>2.128</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
       </c>
       <c r="W11" s="2">
-        <v>0.0113</v>
+        <v>0.0108</v>
       </c>
       <c r="X11" s="2">
-        <v>-0.0019</v>
+        <v>-0.0014</v>
       </c>
       <c r="Y11" s="2">
-        <v>0.0251</v>
+        <v>0.0256</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.116</v>
+        <v>0.1165</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.2721</v>
+        <v>0.2727</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29216.3</v>
+        <v>29265.7</v>
       </c>
       <c r="D12" s="1">
-        <v>20.2</v>
+        <v>69.6</v>
       </c>
       <c r="E12" s="2">
-        <v>0.0007</v>
+        <v>0.0024</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-775.49</v>
+        <v>-726.09</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0259</v>
+        <v>-0.0242</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>436.9</v>
+        <v>486.4</v>
       </c>
       <c r="O12" s="1">
-        <v>149.2</v>
+        <v>197.5</v>
       </c>
       <c r="P12" s="1">
-        <v>-774.39</v>
+        <v>-726.09</v>
       </c>
       <c r="Q12" s="2">
         <v>1</v>
